--- a/waqf-2026/محفظة-الوقف-2026.xlsx
+++ b/waqf-2026/محفظة-الوقف-2026.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="450">
-  <si>
-    <t xml:space="preserve">المحفظة المقترحة لوقف الأسهم — 1,500,000 ريال</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="447">
+  <si>
+    <t xml:space="preserve">المحفظة المعتمدة من مجلس الإدارة — 1,500,000 ريال</t>
   </si>
   <si>
     <t xml:space="preserve">الأسعار: آخر إغلاق على أرقام في 11–12 أكتوبر 2026 · الخلايا الزرقاء مدخلات قابلة للتعديل وتعيد حساب كل شيء تلقائياً</t>
@@ -110,6 +110,15 @@
     <t xml:space="preserve">1.17 (نصف ثاني 2025 بعد تعديل المنحة) + 1.26 (نصف أول 2026)</t>
   </si>
   <si>
+    <t xml:space="preserve">مصرف الإنماء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25/ربع في 2026؛ المتحفظ يفترض منحة بدل نقد في ربع واحد</t>
+  </si>
+  <si>
     <t xml:space="preserve">إس تي سي</t>
   </si>
   <si>
@@ -122,15 +131,6 @@
     <t xml:space="preserve">سياسة معلنة 0.55 ريال/ربع حتى الربع الثالث 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">مصرف الإنماء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25/ربع في 2026؛ المتحفظ يفترض منحة بدل نقد في ربع واحد</t>
-  </si>
-  <si>
     <t xml:space="preserve">أرامكو السعودية</t>
   </si>
   <si>
@@ -143,58 +143,574 @@
     <t xml:space="preserve">توزيع أساسي 0.34/ربع بلا توزيع مرتبط بالأداء</t>
   </si>
   <si>
+    <t xml:space="preserve">النهدي الطبية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرعاية الصحية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60 + 3.00؛ المتحفظ يعكس تراجع الربح 9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سابك للمغذيات الزراعية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المواد الأساسية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50 + 3.50؛ المتحفظ يعكس هبوط ربح الربع الثاني 64%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسمنت السعودية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80 + 1.00؛ مغطى بالأرباح ~76%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المتحدة للإلكترونيات (إكسترا)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التجزئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00 + 3.00؛ مشروط بموافقة الهيئة الشرعية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإجمالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النقد المتبقي بعد الشراء (احتياطي)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العائد النقدي المتوقع — أساسي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العائد النقدي المتوقع — متحفظ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المصروف للجمعية سنوياً — أساسي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المصروف للجمعية سنوياً — متحفظ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المعاد استثماره سنوياً — أساسي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أكبر وزن لسهم واحد (الحد 15%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فحص: مجموع الأوزان = 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التوزيع القطاعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدخل الأساسي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تقييم 28 سهماً وصندوقاً مرشحاً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العائد التاريخي = توزيعات آخر 12 شهراً ÷ السعر · نسبة التوزيع = التوزيعات ÷ صافي الربح · الشرعية: الراجحي المالية / البلاد المالية (31-03-2026) / د. العصيمي (17-08-2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السهم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توزيعات آخر 12 شهراً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العائد التاريخي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توزيعات 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المعلن عن 2026 حتى الآن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمو الربح (النصف الأول 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة التوزيع من الربح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الراجحي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البلاد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العصيمي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">درجة الجودة (من 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السبب الرئيسي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50 (قبل المنحة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+14%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~55%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير مصنف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ضمن المحفظة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أقوى ربحية في السوق، توزيع نصف سنوي متنامٍ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55 + 0.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−2% (+6% دون بنود استثنائية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سياسة توزيع معلنة ثابتة حتى 2027، متوافق في القوائم الثلاث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90 (قبل المنحة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25 + 0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~46%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توزيع ربعي منتظم، نسبة توزيع منخفضة تمنح هامش أمان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنك البلاد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~49%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستبعد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استُبعد بقرار مجلس الإدارة (أكتوبر 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بنك الجزيرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا شيء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">انقطاع التوزيعات 2022–2026 وعدم إعلان توزيع 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عِلم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التقنية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~33%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائد منخفض 1.7% وتذبذب مرتفع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34 + 0.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+33%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~68%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✔ (مختلط)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غير مدرج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توزيع أساسي تصاعدي، لكنه يفوق التدفق النقدي الحر في 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سابك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البتروكيماويات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10 (خُفّض 27%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خسارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يوزع من الميزانية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خسارة 25.8 مليار في 2025 وتخفيض التوزيع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−21%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~77% (2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعلى عائد بين الكبار وميزانية قوية؛ وزن محدود لتذبذب الأسمدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سبكيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أول خسارة سنوية في تاريخه ولا توزيع عن 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المتقدمة للبتروكيماويات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا توزيعات منذ 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ينساب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+364% (قاعدة متدنية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1400% (2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التوزيع أضعاف الربح؛ غير مستدام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~76%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائد مرتفع مغطى بالأرباح؛ وزن صغير للتنويع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسمنت القصيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80 + 0.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−19%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~146%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يوزع أكثر من أرباحه مع اقتراض جديد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أسمنت اليمامة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ربح 265 مليون</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~42%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بديل احتياطي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تغطية ممتازة وعائد متوسط 4.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إكسترا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ضمن المحفظة (مشروط)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائد 9% لكن لديه ذراع تمويل استهلاكي؛ يلزم رأي الهيئة الشرعية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ذيب لتأجير السيارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−45%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توقف التوزيع في 2026 ومديونية مرتفعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الدواء للخدمات الطبية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63 ربع أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−73%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;200%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التوزيع ضعف الأرباح؛ التخفيض مرجح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60 نصف أول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−8.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توزيع ثابت مرتفع وديون منخفضة؛ متوافق في القوائم الثلاث</t>
+  </si>
+  <si>
     <t xml:space="preserve">جرير للتسويق</t>
   </si>
   <si>
     <t xml:space="preserve">4190</t>
   </si>
   <si>
-    <t xml:space="preserve">التجزئة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آخر 4 أرباع؛ المتحفظ −10%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النهدي الطبية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرعاية الصحية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60 + 3.00؛ المتحفظ يعكس تراجع الربح 9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سابك للمغذيات الزراعية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المواد الأساسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50 + 3.50؛ المتحفظ يعكس هبوط ربح الربع الثاني 64%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المتحدة للإلكترونيات (إكسترا)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00 + 3.00؛ مشروط بموافقة الهيئة الشرعية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أسمنت السعودية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80 + 1.00؛ مغطى بالأرباح ~76%</t>
+    <t xml:space="preserve">0.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21 + 0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+18%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بوبا العربية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التأمين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~56%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائد 2.8% وقطاع التأمين محل خلاف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المواساة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~52%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قائمة مراقبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمو جيد لكن العائد 3.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المراعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأغذية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~47%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائد 2.6% ومديونية 14 مليار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سدكو كابيتال ريت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صناديق الريت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1375 + 0.137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFO +43%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مديونية 53% من الأصول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستبعد حالياً</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائد 8.4% لكن مديونية مرتفعة بفائدة متغيرة واستحواذات جديدة</t>
   </si>
   <si>
     <t xml:space="preserve">جدوى ريت السعودية</t>
@@ -203,10 +719,16 @@
     <t xml:space="preserve">4342</t>
   </si>
   <si>
-    <t xml:space="preserve">صناديق الريت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20/ربع ثابتة منذ 2024</t>
+    <t xml:space="preserve">0.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20 + 0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثابت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يوزع 131% من دخله التشغيلي (FFO)؛ التوزيع غير مغطى</t>
   </si>
   <si>
     <t xml:space="preserve">الراجحي ريت</t>
@@ -215,537 +737,6 @@
     <t xml:space="preserve">4340</t>
   </si>
   <si>
-    <t xml:space="preserve">توزيعات 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الإجمالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النقد المتبقي بعد الشراء (احتياطي)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العائد النقدي المتوقع — أساسي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العائد النقدي المتوقع — متحفظ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المصروف للجمعية سنوياً — أساسي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المصروف للجمعية سنوياً — متحفظ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المعاد استثماره سنوياً — أساسي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أكبر وزن لسهم واحد (الحد 15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فحص: مجموع الأوزان = 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التوزيع القطاعي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدخل الأساسي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تقييم 28 سهماً وصندوقاً مرشحاً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العائد التاريخي = توزيعات آخر 12 شهراً ÷ السعر · نسبة التوزيع = التوزيعات ÷ صافي الربح · الشرعية: الراجحي المالية / البلاد المالية (31-03-2026) / د. العصيمي (17-08-2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السهم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">توزيعات آخر 12 شهراً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العائد التاريخي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المعلن عن 2026 حتى الآن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نمو الربح (النصف الأول 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة التوزيع من الربح</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الراجحي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البلاد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العصيمي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">درجة الجودة (من 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القرار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السبب الرئيسي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50 (قبل المنحة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+14%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~55%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غير مصنف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ضمن المحفظة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أقوى ربحية في السوق، توزيع نصف سنوي متنامٍ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55 + 0.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−2% (+6% دون بنود استثنائية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سياسة توزيع معلنة ثابتة حتى 2027، متوافق في القوائم الثلاث</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90 (قبل المنحة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25 + 0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~46%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">توزيع ربعي منتظم، نسبة توزيع منخفضة تمنح هامش أمان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بنك البلاد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~49%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بديل احتياطي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نمو بطيء وتراجع السعر 16% خلال 6 أشهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بنك الجزيرة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا شيء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مستبعد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">انقطاع التوزيعات 2022–2026 وعدم إعلان توزيع 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عِلم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التقنية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~33%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عائد منخفض 1.7% وتذبذب مرتفع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34 + 0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+33%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~68%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✔ (مختلط)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غير مدرج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">توزيع أساسي تصاعدي، لكنه يفوق التدفق النقدي الحر في 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سابك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البتروكيماويات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10 (خُفّض 27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خسارة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يوزع من الميزانية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خسارة 25.8 مليار في 2025 وتخفيض التوزيع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−21%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~77% (2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أعلى عائد بين الكبار وميزانية قوية؛ وزن محدود لتذبذب الأسمدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سبكيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أول خسارة سنوية في تاريخه ولا توزيع عن 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المتقدمة للبتروكيماويات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا توزيعات منذ 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ينساب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+364% (قاعدة متدنية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1400% (2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التوزيع أضعاف الربح؛ غير مستدام</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~76%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عائد مرتفع مغطى بالأرباح؛ وزن صغير للتنويع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أسمنت القصيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80 + 0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−19%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~146%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يوزع أكثر من أرباحه مع اقتراض جديد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أسمنت اليمامة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ربح 265 مليون</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~42%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تغطية ممتازة وعائد متوسط 4.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إكسترا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~80%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ضمن المحفظة (مشروط)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عائد 9% لكن لديه ذراع تمويل استهلاكي؛ يلزم رأي الهيئة الشرعية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ذيب لتأجير السيارات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">النقل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−45%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">توقف التوزيع في 2026 ومديونية مرتفعة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدواء للخدمات الطبية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 ربع أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−73%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;200%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التوزيع ضعف الأرباح؛ التخفيض مرجح</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60 نصف أول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−8.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">توزيع ثابت مرتفع وديون منخفضة؛ متوافق في القوائم الثلاث</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21 + 0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+18%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أفضل زخم أرباح، ديون منخفضة، توزيع ربعي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بوبا العربية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التأمين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~56%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عائد 2.8% وقطاع التأمين محل خلاف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المواساة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~52%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قائمة مراقبة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نمو جيد لكن العائد 3.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المراعي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأغذية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~47%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عائد 2.6% ومديونية 14 مليار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سدكو كابيتال ريت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1375 + 0.137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFO +43%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مديونية 53% من الأصول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مستبعد حالياً</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عائد 8.4% لكن مديونية مرتفعة بفائدة متغيرة واستحواذات جديدة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20 + 0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ثابت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أكثر صناديق الريت ثباتاً: 0.20 كل ربع منذ 2024</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.52</t>
   </si>
   <si>
@@ -755,7 +746,7 @@
     <t xml:space="preserve">مستقر</t>
   </si>
   <si>
-    <t xml:space="preserve">توزيع ربعي مستقر من مدير متوافق</t>
+    <t xml:space="preserve">اقتصرت المحفظة على الأسهم؛ التوزيع ~101% من FFO</t>
   </si>
   <si>
     <t xml:space="preserve">الرياض ريت</t>
@@ -962,7 +953,7 @@
     <t xml:space="preserve">تخفيض شركة لتوزيعاتها (كما حدث في سابك وذيب والدواء)</t>
   </si>
   <si>
-    <t xml:space="preserve">تنويع على 11 مركزاً، لا يتجاوز سهم 15%، استبعاد من يوزع أكثر من أرباحه</t>
+    <t xml:space="preserve">تنويع على 8 أسهم و6 قطاعات، لا يتجاوز سهم 15%، استبعاد من يوزع أكثر من أرباحه</t>
   </si>
   <si>
     <t xml:space="preserve">نسبة التوزيع &gt; 100% لربعين</t>
@@ -980,7 +971,7 @@
     <t xml:space="preserve">ارتفاع الفائدة (رفع ساما في سبتمبر 2026) يضغط على البنوك والريت</t>
   </si>
   <si>
-    <t xml:space="preserve">اختيار ريت منخفض المديونية واستبعاد سدكو ريت حالياً</t>
+    <t xml:space="preserve">تنويع على 6 قطاعات؛ البنوك 25% فقط</t>
   </si>
   <si>
     <t xml:space="preserve">سايبور 3 أشهر &gt; 5.5%</t>
@@ -989,7 +980,7 @@
     <t xml:space="preserve">تقلب أسعار النفط والأسمدة (أرامكو، سابك للمغذيات)</t>
   </si>
   <si>
-    <t xml:space="preserve">حصر القطاع عند 18% من المحفظة</t>
+    <t xml:space="preserve">حصر الطاقة والأسمدة عند 27% من المحفظة</t>
   </si>
   <si>
     <t xml:space="preserve">تراجع خام برنت أو أسعار اليوريا &gt; 20%</t>
@@ -1058,7 +1049,7 @@
     <t xml:space="preserve">الأدوات المسموحة</t>
   </si>
   <si>
-    <t xml:space="preserve">أسهم سعودية متوافقة شرعياً + صناديق ريت متوافقة بحد أقصى 15%</t>
+    <t xml:space="preserve">أسهم سعودية متوافقة شرعياً (8 أسهم معتمدة من مجلس الإدارة)</t>
   </si>
   <si>
     <t xml:space="preserve">طلب المتبرع + تنويع مصدر الدخل</t>
@@ -1202,7 +1193,7 @@
     <t xml:space="preserve">أرقام</t>
   </si>
   <si>
-    <t xml:space="preserve">عائد المحفظة المقترحة — أساسي</t>
+    <t xml:space="preserve">عائد المحفظة المعتمدة — أساسي</t>
   </si>
   <si>
     <t xml:space="preserve">محسوب</t>
@@ -1520,7 +1511,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF8A6D00"/>
+      <color rgb="FFB3261E"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1528,7 +1519,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FFB3261E"/>
+      <color rgb="FF8A6D00"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1786,15 +1777,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1881,12 +1872,12 @@
       <rgbColor rgb="FF1B7F4C"/>
       <rgbColor rgb="FFC8D1CC"/>
       <rgbColor rgb="FF878787"/>
-      <rgbColor rgb="FF93A9CE"/>
-      <rgbColor rgb="FFAB4744"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FFFFF4C2"/>
       <rgbColor rgb="FFEEF3F1"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFDC853E"/>
+      <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1155CC"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
@@ -1895,7 +1886,7 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF5F6F7"/>
@@ -1905,20 +1896,20 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF6C7C3"/>
-      <rgbColor rgb="FF4672A8"/>
-      <rgbColor rgb="FF4299B0"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF4BACC6"/>
+      <rgbColor rgb="FF9BBB59"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF79646"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF725990"/>
-      <rgbColor rgb="FF8AA64F"/>
+      <rgbColor rgb="FF8064A2"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF1F3A5F"/>
       <rgbColor rgb="FF2E7D6B"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FFB3261E"/>
-      <rgbColor rgb="FFC0504D"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF555555"/>
     </indexedColors>
@@ -1974,7 +1965,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'المحفظة المقترحة'!D33</c:f>
+              <c:f>'المحفظة المقترحة'!D30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1996,7 +1987,7 @@
             <c:idx val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4672a8"/>
+                <a:srgbClr val="4f81bd"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
@@ -2007,7 +1998,7 @@
             <c:idx val="1"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ab4744"/>
+                <a:srgbClr val="c0504d"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
@@ -2018,7 +2009,7 @@
             <c:idx val="2"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="8aa64f"/>
+                <a:srgbClr val="9bbb59"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
@@ -2029,7 +2020,7 @@
             <c:idx val="3"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="725990"/>
+                <a:srgbClr val="8064a2"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
@@ -2040,7 +2031,7 @@
             <c:idx val="4"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4299b0"/>
+                <a:srgbClr val="4bacc6"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
@@ -2051,18 +2042,7 @@
             <c:idx val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="dc853e"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="93a9ce"/>
+                <a:srgbClr val="f79646"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
@@ -2214,30 +2194,6 @@
               <c:showPercent val="1"/>
               <c:separator>; </c:separator>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Calibri"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -2263,9 +2219,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'المحفظة المقترحة'!$C$34:$C$40</c:f>
+              <c:f>'المحفظة المقترحة'!$C$31:$C$36</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>البنوك</c:v>
                 </c:pt>
@@ -2284,38 +2240,32 @@
                 <c:pt idx="5">
                   <c:v>المواد الأساسية</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>صناديق الريت</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'المحفظة المقترحة'!$D$34:$D$40</c:f>
+              <c:f>'المحفظة المقترحة'!$D$31:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.23</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.17</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1</c:v>
+                  <c:v>0.13</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.12</c:v>
+                  <c:v>0.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2469,83 +2419,65 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'المحفظة المقترحة'!$C$10:$C$20</c:f>
+              <c:f>'المحفظة المقترحة'!$C$10:$C$17</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>مصرف الراجحي</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>إس تي سي</c:v>
+                  <c:v>مصرف الإنماء</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>مصرف الإنماء</c:v>
+                  <c:v>إس تي سي</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>أرامكو السعودية</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>جرير للتسويق</c:v>
+                  <c:v>النهدي الطبية</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>النهدي الطبية</c:v>
+                  <c:v>سابك للمغذيات الزراعية</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>سابك للمغذيات الزراعية</c:v>
+                  <c:v>أسمنت السعودية</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>المتحدة للإلكترونيات (إكسترا)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>أسمنت السعودية</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>جدوى ريت السعودية</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>الراجحي ريت</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'المحفظة المقترحة'!$M$10:$M$20</c:f>
+              <c:f>'المحفظة المقترحة'!$M$10:$M$17</c:f>
               <c:numCache>
                 <c:formatCode>#,##0" ر.س"</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8808.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>6337</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>11704</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>5069</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>7905.68</c:v>
+                  <c:v>11857.84</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10655.2</c:v>
+                  <c:v>12180</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9368.8</c:v>
+                  <c:v>10906</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7266</c:v>
+                  <c:v>10303.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6720</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5151.6</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8648.8</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5997.16</c:v>
+                  <c:v>13440</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2604,83 +2536,65 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'المحفظة المقترحة'!$C$10:$C$20</c:f>
+              <c:f>'المحفظة المقترحة'!$C$10:$C$17</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>مصرف الراجحي</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>إس تي سي</c:v>
+                  <c:v>مصرف الإنماء</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>مصرف الإنماء</c:v>
+                  <c:v>إس تي سي</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>أرامكو السعودية</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>جرير للتسويق</c:v>
+                  <c:v>النهدي الطبية</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>النهدي الطبية</c:v>
+                  <c:v>سابك للمغذيات الزراعية</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>سابك للمغذيات الزراعية</c:v>
+                  <c:v>أسمنت السعودية</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>المتحدة للإلكترونيات (إكسترا)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>أسمنت السعودية</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>جدوى ريت السعودية</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>الراجحي ريت</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'المحفظة المقترحة'!$N$10:$N$20</c:f>
+              <c:f>'المحفظة المقترحة'!$N$10:$N$17</c:f>
               <c:numCache>
                 <c:formatCode>#,##0" ر.س"</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8808.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4752.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>11704</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>3801.75</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>7905.68</c:v>
+                  <c:v>11857.84</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9533.6</c:v>
+                  <c:v>10875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8365</c:v>
+                  <c:v>8569</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5709</c:v>
+                  <c:v>9158.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5376</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4579.2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7783.92</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5535.84</c:v>
+                  <c:v>10752</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2688,11 +2602,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39569961"/>
-        <c:axId val="84129720"/>
+        <c:axId val="97491667"/>
+        <c:axId val="36363071"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39569961"/>
+        <c:axId val="97491667"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2724,7 +2638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84129720"/>
+        <c:crossAx val="36363071"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2732,7 +2646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84129720"/>
+        <c:axId val="36363071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2774,7 +2688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39569961"/>
+        <c:crossAx val="97491667"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2832,13 +2746,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>-725040</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>136440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2847,7 +2761,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="-9042120" y="6410160"/>
+        <a:off x="-9042120" y="5838840"/>
         <a:ext cx="4319640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2862,14 +2776,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>-1812600</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>115200</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>115560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2877,7 +2791,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="-14993280" y="6410160"/>
+        <a:off x="-14993280" y="5838840"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3089,7 +3003,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:P40"/>
+  <dimension ref="B2:P36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3321,46 +3235,46 @@
         <v>28</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="20" t="n">
         <f aca="false">$E$5*F11</f>
-        <v>225000</v>
+        <v>150000</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>42.22</v>
+        <v>23.63</v>
       </c>
       <c r="I11" s="22" t="n">
         <f aca="false">ROUNDDOWN(G11/(H11*(1+$E$7)),0)</f>
-        <v>5320</v>
+        <v>6337</v>
       </c>
       <c r="J11" s="20" t="n">
         <f aca="false">I11*H11*(1+$E$7)</f>
-        <v>224992.23768</v>
+        <v>149997.873627</v>
       </c>
       <c r="K11" s="21" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="21" t="n">
-        <v>2.2</v>
+        <v>0.75</v>
       </c>
       <c r="M11" s="20" t="n">
         <f aca="false">I11*K11</f>
-        <v>11704</v>
+        <v>6337</v>
       </c>
       <c r="N11" s="20" t="n">
         <f aca="false">I11*L11</f>
-        <v>11704</v>
+        <v>4752.75</v>
       </c>
       <c r="O11" s="23" t="n">
         <f aca="false">IFERROR(M11/J11,0)</f>
-        <v>0.0520195724114103</v>
+        <v>0.0422472655562987</v>
       </c>
       <c r="P11" s="24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3368,49 +3282,49 @@
         <v>3</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="F12" s="11" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">$E$5*F12</f>
-        <v>120000</v>
+        <v>225000</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>23.63</v>
+        <v>42.22</v>
       </c>
       <c r="I12" s="14" t="n">
         <f aca="false">ROUNDDOWN(G12/(H12*(1+$E$7)),0)</f>
-        <v>5069</v>
+        <v>5320</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">I12*H12*(1+$E$7)</f>
-        <v>119984.096799</v>
+        <v>224992.23768</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0.75</v>
+        <v>2.2</v>
       </c>
       <c r="M12" s="12" t="n">
         <f aca="false">I12*K12</f>
-        <v>5069</v>
+        <v>11704</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">I12*L12</f>
-        <v>3801.75</v>
+        <v>11704</v>
       </c>
       <c r="O12" s="15" t="n">
         <f aca="false">IFERROR(M12/J12,0)</f>
-        <v>0.0422472655562987</v>
+        <v>0.0520195724114103</v>
       </c>
       <c r="P12" s="16" t="s">
         <v>33</v>
@@ -3430,22 +3344,22 @@
         <v>36</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="20" t="n">
         <f aca="false">$E$5*F13</f>
-        <v>150000</v>
+        <v>225000</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>25.76</v>
       </c>
       <c r="I13" s="22" t="n">
         <f aca="false">ROUNDDOWN(G13/(H13*(1+$E$7)),0)</f>
-        <v>5813</v>
+        <v>8719</v>
       </c>
       <c r="J13" s="20" t="n">
         <f aca="false">I13*H13*(1+$E$7)</f>
-        <v>149997.442896</v>
+        <v>224983.262448</v>
       </c>
       <c r="K13" s="21" t="n">
         <v>1.36</v>
@@ -3455,15 +3369,15 @@
       </c>
       <c r="M13" s="20" t="n">
         <f aca="false">I13*K13</f>
-        <v>7905.68</v>
+        <v>11857.84</v>
       </c>
       <c r="N13" s="20" t="n">
         <f aca="false">I13*L13</f>
-        <v>7905.68</v>
+        <v>11857.84</v>
       </c>
       <c r="O13" s="23" t="n">
         <f aca="false">IFERROR(M13/J13,0)</f>
-        <v>0.0527054318218035</v>
+        <v>0.0527054318218036</v>
       </c>
       <c r="P13" s="24" t="s">
         <v>37</v>
@@ -3483,40 +3397,40 @@
         <v>40</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G14" s="12" t="n">
         <f aca="false">$E$5*F14</f>
-        <v>180000</v>
+        <v>195000</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>16.02</v>
+        <v>89.5</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">ROUNDDOWN(G14/(H14*(1+$E$7)),0)</f>
-        <v>11216</v>
+        <v>2175</v>
       </c>
       <c r="J14" s="12" t="n">
         <f aca="false">I14*H14*(1+$E$7)</f>
-        <v>179985.776544</v>
+        <v>194993.42625</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0.95</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0.85</v>
+        <v>5</v>
       </c>
       <c r="M14" s="12" t="n">
         <f aca="false">I14*K14</f>
-        <v>10655.2</v>
+        <v>12180</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">I14*L14</f>
-        <v>9533.6</v>
+        <v>10875</v>
       </c>
       <c r="O14" s="15" t="n">
         <f aca="false">IFERROR(M14/J14,0)</f>
-        <v>0.0592002335106474</v>
+        <v>0.0624636442070826</v>
       </c>
       <c r="P14" s="16" t="s">
         <v>41</v>
@@ -3536,40 +3450,40 @@
         <v>44</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G15" s="20" t="n">
         <f aca="false">$E$5*F15</f>
-        <v>150000</v>
+        <v>180000</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>89.5</v>
+        <v>115.3</v>
       </c>
       <c r="I15" s="22" t="n">
         <f aca="false">ROUNDDOWN(G15/(H15*(1+$E$7)),0)</f>
-        <v>1673</v>
+        <v>1558</v>
       </c>
       <c r="J15" s="20" t="n">
         <f aca="false">I15*H15*(1+$E$7)</f>
-        <v>149988.04695</v>
+        <v>179942.78358</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="L15" s="21" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M15" s="20" t="n">
         <f aca="false">I15*K15</f>
-        <v>9368.8</v>
+        <v>10906</v>
       </c>
       <c r="N15" s="20" t="n">
         <f aca="false">I15*L15</f>
-        <v>8365</v>
+        <v>8569</v>
       </c>
       <c r="O15" s="23" t="n">
         <f aca="false">IFERROR(M15/J15,0)</f>
-        <v>0.0624636442070826</v>
+        <v>0.0606081543423015</v>
       </c>
       <c r="P15" s="24" t="s">
         <v>45</v>
@@ -3586,46 +3500,46 @@
         <v>47</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="12" t="n">
         <f aca="false">$E$5*F16</f>
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>115.3</v>
+        <v>26.16</v>
       </c>
       <c r="I16" s="14" t="n">
         <f aca="false">ROUNDDOWN(G16/(H16*(1+$E$7)),0)</f>
-        <v>1038</v>
+        <v>5724</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">I16*H16*(1+$E$7)</f>
-        <v>119884.85838</v>
+        <v>149994.397728</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="M16" s="12" t="n">
         <f aca="false">I16*K16</f>
-        <v>7266</v>
+        <v>10303.2</v>
       </c>
       <c r="N16" s="12" t="n">
         <f aca="false">I16*L16</f>
-        <v>5709</v>
+        <v>9158.4</v>
       </c>
       <c r="O16" s="15" t="n">
         <f aca="false">IFERROR(M16/J16,0)</f>
-        <v>0.0606081543423015</v>
+        <v>0.0686905654882113</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3633,31 +3547,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="E17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>40</v>
-      </c>
       <c r="F17" s="19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="20" t="n">
         <f aca="false">$E$5*F17</f>
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>55.7</v>
       </c>
       <c r="I17" s="22" t="n">
         <f aca="false">ROUNDDOWN(G17/(H17*(1+$E$7)),0)</f>
-        <v>1344</v>
+        <v>2688</v>
       </c>
       <c r="J17" s="20" t="n">
         <f aca="false">I17*H17*(1+$E$7)</f>
-        <v>74988.06336</v>
+        <v>149976.12672</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>5</v>
@@ -3667,11 +3581,11 @@
       </c>
       <c r="M17" s="20" t="n">
         <f aca="false">I17*K17</f>
-        <v>6720</v>
+        <v>13440</v>
       </c>
       <c r="N17" s="20" t="n">
         <f aca="false">I17*L17</f>
-        <v>5376</v>
+        <v>10752</v>
       </c>
       <c r="O17" s="23" t="n">
         <f aca="false">IFERROR(M17/J17,0)</f>
@@ -3682,404 +3596,232 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="26" t="n">
+        <f aca="false">SUM(F10:F17)</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <f aca="false">SUM(G10:G17)</f>
+        <v>1500000</v>
+      </c>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="27" t="n">
+        <f aca="false">SUM(J10:J17)</f>
+        <v>1499830.624908</v>
+      </c>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="27" t="n">
+        <f aca="false">SUM(M10:M17)</f>
+        <v>85536.79</v>
+      </c>
+      <c r="N18" s="27" t="n">
+        <f aca="false">SUM(N10:N17)</f>
+        <v>76477.74</v>
+      </c>
+      <c r="O18" s="26" t="n">
+        <f aca="false">IFERROR(M18/J18,0)</f>
+        <v>0.0570309664167891</v>
+      </c>
+      <c r="P18" s="25"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <f aca="false">$E$5*F18</f>
-        <v>75000</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <f aca="false">ROUNDDOWN(G18/(H18*(1+$E$7)),0)</f>
-        <v>2862</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <f aca="false">I18*H18*(1+$E$7)</f>
-        <v>74997.198864</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <f aca="false">I18*K18</f>
-        <v>5151.6</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <f aca="false">I18*L18</f>
-        <v>4579.2</v>
-      </c>
-      <c r="O18" s="15" t="n">
-        <f aca="false">IFERROR(M18/J18,0)</f>
-        <v>0.0686905654882113</v>
-      </c>
-      <c r="P18" s="16" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="28" t="n">
+        <f aca="false">E5-J18</f>
+        <v>169.375092000002</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C21" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="C19" s="18" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="29" t="n">
+        <f aca="false">M18/E5</f>
+        <v>0.0570245266666667</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <f aca="false">$E$5*F19</f>
-        <v>90000</v>
-      </c>
-      <c r="H19" s="21" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="I19" s="22" t="n">
-        <f aca="false">ROUNDDOWN(G19/(H19*(1+$E$7)),0)</f>
-        <v>10811</v>
-      </c>
-      <c r="J19" s="20" t="n">
-        <f aca="false">I19*H19*(1+$E$7)</f>
-        <v>89992.136997</v>
-      </c>
-      <c r="K19" s="21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="M19" s="20" t="n">
-        <f aca="false">I19*K19</f>
-        <v>8648.8</v>
-      </c>
-      <c r="N19" s="20" t="n">
-        <f aca="false">I19*L19</f>
-        <v>7783.92</v>
-      </c>
-      <c r="O19" s="23" t="n">
-        <f aca="false">IFERROR(M19/J19,0)</f>
-        <v>0.0961061742570722</v>
-      </c>
-      <c r="P19" s="24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <f aca="false">$E$5*F20</f>
-        <v>90000</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <f aca="false">ROUNDDOWN(G20/(H20*(1+$E$7)),0)</f>
-        <v>11533</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <f aca="false">I20*H20*(1+$E$7)</f>
-        <v>89994.801519</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <f aca="false">I20*K20</f>
-        <v>5997.16</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <f aca="false">I20*L20</f>
-        <v>5535.84</v>
-      </c>
-      <c r="O20" s="15" t="n">
-        <f aca="false">IFERROR(M20/J20,0)</f>
-        <v>0.0666389602374295</v>
-      </c>
-      <c r="P20" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="25"/>
-      <c r="C21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26" t="n">
-        <f aca="false">SUM(F10:F20)</f>
-        <v>1</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <f aca="false">SUM(G10:G20)</f>
-        <v>1500000</v>
-      </c>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="27" t="n">
-        <f aca="false">SUM(J10:J20)</f>
-        <v>1499755.176864</v>
-      </c>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="27" t="n">
-        <f aca="false">SUM(M10:M20)</f>
-        <v>87294.99</v>
-      </c>
-      <c r="N21" s="27" t="n">
-        <f aca="false">SUM(N10:N20)</f>
-        <v>79102.74</v>
-      </c>
-      <c r="O21" s="26" t="n">
-        <f aca="false">IFERROR(M21/J21,0)</f>
-        <v>0.0582061601431072</v>
-      </c>
-      <c r="P21" s="25"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="29" t="n">
+        <f aca="false">N18/E5</f>
+        <v>0.05098516</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="28" t="n">
-        <f aca="false">E5-J21</f>
-        <v>244.823135999963</v>
+        <f aca="false">M18*E6</f>
+        <v>68429.432</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="29" t="n">
-        <f aca="false">M21/E5</f>
-        <v>0.05819666</v>
+      <c r="G24" s="28" t="n">
+        <f aca="false">N18*E6</f>
+        <v>61182.192</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="29" t="n">
-        <f aca="false">N21/E5</f>
-        <v>0.05273516</v>
+      <c r="G25" s="28" t="n">
+        <f aca="false">M18*(1-E6)</f>
+        <v>17107.358</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="28" t="n">
-        <f aca="false">M21*E6</f>
-        <v>69835.992</v>
+      <c r="G26" s="29" t="n">
+        <f aca="false">MAX(F10:F17)</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="28" t="n">
-        <f aca="false">N21*E6</f>
-        <v>63282.192</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="28" t="n">
-        <f aca="false">M21*(1-E6)</f>
-        <v>17458.998</v>
+      <c r="G27" s="30" t="str">
+        <f aca="false">IF(ROUND(F18,4)=1,"سليم","راجع الأوزان")</f>
+        <v>سليم</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="29" t="n">
-        <f aca="false">MAX(F10:F20)</f>
+      <c r="C29" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+    </row>
+    <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <f aca="false">SUMIF($E$10:$E$17,C31,$F$10:$F$17)</f>
+        <v>0.25</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <f aca="false">SUMIF($E$10:$E$17,C31,$M$10:$M$17)</f>
+        <v>15145.75</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <f aca="false">SUMIF($E$10:$E$17,C32,$F$10:$F$17)</f>
         <v>0.15</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="30" t="str">
-        <f aca="false">IF(ROUND(F21,4)=1,"سليم","راجع الأوزان")</f>
-        <v>سليم</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C32" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-    </row>
-    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C33" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>73</v>
+      <c r="E32" s="12" t="n">
+        <f aca="false">SUMIF($E$10:$E$17,C32,$M$10:$M$17)</f>
+        <v>11704</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <f aca="false">SUMIF($E$10:$E$17,C33,$F$10:$F$17)</f>
+        <v>0.15</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <f aca="false">SUMIF($E$10:$E$17,C33,$M$10:$M$17)</f>
+        <v>11857.84</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="32" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D34" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C34,$F$10:$F$20)</f>
-        <v>0.23</v>
+        <f aca="false">SUMIF($E$10:$E$17,C34,$F$10:$F$17)</f>
+        <v>0.1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C34,$M$10:$M$20)</f>
-        <v>13877.75</v>
+        <f aca="false">SUMIF($E$10:$E$17,C34,$M$10:$M$17)</f>
+        <v>13440</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="32" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D35" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C35,$F$10:$F$20)</f>
-        <v>0.15</v>
+        <f aca="false">SUMIF($E$10:$E$17,C35,$F$10:$F$17)</f>
+        <v>0.13</v>
       </c>
       <c r="E35" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C35,$M$10:$M$20)</f>
-        <v>11704</v>
+        <f aca="false">SUMIF($E$10:$E$17,C35,$M$10:$M$17)</f>
+        <v>12180</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="32" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D36" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C36,$F$10:$F$20)</f>
-        <v>0.1</v>
+        <f aca="false">SUMIF($E$10:$E$17,C36,$F$10:$F$17)</f>
+        <v>0.22</v>
       </c>
       <c r="E36" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C36,$M$10:$M$20)</f>
-        <v>7905.68</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C37,$F$10:$F$20)</f>
-        <v>0.17</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C37,$M$10:$M$20)</f>
-        <v>17375.2</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C38,$F$10:$F$20)</f>
-        <v>0.1</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C38,$M$10:$M$20)</f>
-        <v>9368.8</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C39,$F$10:$F$20)</f>
-        <v>0.13</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C39,$M$10:$M$20)</f>
-        <v>12417.6</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C40,$F$10:$F$20)</f>
-        <v>0.12</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <f aca="false">SUMIF($E$10:$E$20,C40,$M$10:$M$20)</f>
-        <v>14645.96</v>
+        <f aca="false">SUMIF($E$10:$E$17,C36,$M$10:$M$17)</f>
+        <v>21209.2</v>
       </c>
     </row>
   </sheetData>
@@ -4092,15 +3834,15 @@
     <mergeCell ref="F6:O6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="F7:O7"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C29:E29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4140,7 +3882,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4160,7 +3902,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4180,7 +3922,7 @@
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>10</v>
@@ -4192,40 +3934,40 @@
         <v>14</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4249,45 +3991,45 @@
         <v>0.039225181598063</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="O6" s="9" t="n">
         <v>5</v>
       </c>
       <c r="P6" s="33" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="32" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>42.22</v>
@@ -4300,42 +4042,42 @@
         <v>0.0521080056845097</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O7" s="17" t="n">
         <v>5</v>
       </c>
       <c r="P7" s="34" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="35" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>25</v>
@@ -4351,42 +4093,42 @@
         <v>0.0317393144308083</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>4</v>
       </c>
       <c r="P8" s="33" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="32" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>25</v>
@@ -4402,42 +4144,42 @@
         <v>0.0468123049487294</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="O9" s="17" t="n">
         <v>3</v>
       </c>
       <c r="P9" s="36" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="Q9" s="35" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>25</v>
@@ -4453,45 +4195,45 @@
         <v>0.0440528634361234</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="O10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="Q10" s="32" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>568.5</v>
@@ -4504,34 +4246,34 @@
         <v>0.0167106420404573</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="P11" s="38" t="s">
-        <v>119</v>
+      <c r="P11" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q11" s="35" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4555,45 +4297,45 @@
         <v>0.0524068322981367</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="P12" s="33" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q12" s="32" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E13" s="21" t="n">
         <v>45.7</v>
@@ -4606,45 +4348,45 @@
         <v>0.0568927789934355</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="P13" s="38" t="s">
-        <v>119</v>
+      <c r="P13" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q13" s="35" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>115.3</v>
@@ -4657,45 +4399,45 @@
         <v>0.0607111882046834</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="P14" s="33" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="32" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E15" s="21" t="n">
         <v>11.9</v>
@@ -4708,45 +4450,45 @@
         <v>0.0420168067226891</v>
       </c>
       <c r="H15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>117</v>
-      </c>
       <c r="J15" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="K15" s="17" t="s">
-        <v>151</v>
-      </c>
       <c r="L15" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="P15" s="38" t="s">
-        <v>119</v>
+      <c r="P15" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q15" s="35" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>22.33</v>
@@ -4759,45 +4501,45 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J16" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>151</v>
-      </c>
       <c r="L16" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O16" s="9" t="n">
         <v>1</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="Q16" s="32" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>33.24</v>
@@ -4810,45 +4552,45 @@
         <v>0.0601684717208183</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O17" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="38" t="s">
-        <v>119</v>
+      <c r="P17" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q17" s="35" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>26.16</v>
@@ -4861,45 +4603,45 @@
         <v>0.0688073394495413</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O18" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P18" s="33" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="32" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>43.6</v>
@@ -4912,45 +4654,45 @@
         <v>0.073394495412844</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="P19" s="38" t="s">
-        <v>119</v>
+      <c r="P19" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q19" s="35" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="10" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>21</v>
@@ -4963,45 +4705,45 @@
         <v>0.0476190476190476</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="P20" s="39" t="s">
-        <v>112</v>
+      <c r="P20" s="38" t="s">
+        <v>168</v>
       </c>
       <c r="Q20" s="32" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="18" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>40</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>55.7</v>
@@ -5014,45 +4756,45 @@
         <v>0.0897666068222621</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O21" s="17" t="n">
         <v>3</v>
       </c>
       <c r="P21" s="34" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="Q21" s="35" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="10" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>17.82</v>
@@ -5065,45 +4807,45 @@
         <v>0.0375982042648709</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="Q22" s="32" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>34.68</v>
@@ -5116,45 +4858,45 @@
         <v>0.0726643598615917</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O23" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="P23" s="38" t="s">
-        <v>119</v>
+      <c r="P23" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q23" s="35" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>89.5</v>
@@ -5167,45 +4909,45 @@
         <v>0.0625698324022346</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>4</v>
       </c>
       <c r="P24" s="33" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q24" s="32" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="18" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>39</v>
+        <v>195</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>16.02</v>
@@ -5218,45 +4960,45 @@
         <v>0.0593008739076155</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O25" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="P25" s="34" t="s">
-        <v>94</v>
+      <c r="P25" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q25" s="35" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>141.3</v>
@@ -5269,45 +5011,45 @@
         <v>0.0283085633404105</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O26" s="9" t="n">
         <v>2</v>
       </c>
       <c r="P26" s="37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="Q26" s="32" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>62.35</v>
@@ -5320,45 +5062,45 @@
         <v>0.0341619887730553</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O27" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="P27" s="36" t="s">
-        <v>219</v>
+      <c r="P27" s="39" t="s">
+        <v>211</v>
       </c>
       <c r="Q27" s="35" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="10" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>43.5</v>
@@ -5371,45 +5113,45 @@
         <v>0.0264367816091954</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O28" s="9" t="n">
         <v>2</v>
       </c>
       <c r="P28" s="37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="32" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>6.65</v>
@@ -5422,45 +5164,45 @@
         <v>0.083609022556391</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O29" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="P29" s="38" t="s">
-        <v>233</v>
+      <c r="P29" s="36" t="s">
+        <v>226</v>
       </c>
       <c r="Q29" s="35" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
-        <v>56</v>
+        <v>228</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>8.31</v>
@@ -5473,45 +5215,45 @@
         <v>0.0962695547533093</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O30" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="P30" s="33" t="s">
-        <v>94</v>
+      <c r="P30" s="37" t="s">
+        <v>103</v>
       </c>
       <c r="Q30" s="32" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>7.79</v>
@@ -5524,45 +5266,45 @@
         <v>0.0693196405648267</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M31" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O31" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="P31" s="34" t="s">
-        <v>94</v>
+      <c r="P31" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q31" s="35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>4.31</v>
@@ -5575,45 +5317,45 @@
         <v>0.074245939675174</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O32" s="9" t="n">
         <v>2</v>
       </c>
       <c r="P32" s="37" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="Q32" s="32" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>4.47</v>
@@ -5626,34 +5368,34 @@
         <v>0.0782997762863535</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O33" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="P33" s="38" t="s">
-        <v>119</v>
+      <c r="P33" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="Q33" s="35" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5696,7 +5438,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5708,7 +5450,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5723,25 +5465,25 @@
         <v>8</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>259</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5749,10 +5491,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E6" s="40" t="n">
         <v>46308</v>
@@ -5761,13 +5503,13 @@
         <v>46315</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5775,10 +5517,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>46308</v>
@@ -5787,13 +5529,13 @@
         <v>46317</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5801,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E8" s="40" t="n">
         <v>46309</v>
@@ -5813,13 +5555,13 @@
         <v>46320</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5827,10 +5569,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>46315</v>
@@ -5839,13 +5581,13 @@
         <v>46341</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5853,10 +5595,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E10" s="40" t="n">
         <v>46321</v>
@@ -5865,13 +5607,13 @@
         <v>46328</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5879,10 +5621,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>46322</v>
@@ -5891,13 +5633,13 @@
         <v>46338</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5905,10 +5647,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E12" s="40" t="n">
         <v>46341</v>
@@ -5917,13 +5659,13 @@
         <v>46371</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5931,10 +5673,10 @@
         <v>8</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>46402</v>
@@ -5943,13 +5685,13 @@
         <v>46418</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5957,10 +5699,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E14" s="40" t="n">
         <v>46447</v>
@@ -5969,13 +5711,13 @@
         <v>46477</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5983,10 +5725,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>46478</v>
@@ -5995,18 +5737,18 @@
         <v>46507</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D17" s="43" t="n">
         <f aca="false">COUNTIF(G6:G15,"مكتمل")/COUNTA(G6:G15)</f>
@@ -6052,7 +5794,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6063,7 +5805,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -6077,22 +5819,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>306</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6100,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D6" s="44" t="n">
         <v>3</v>
@@ -6113,10 +5855,10 @@
         <v>9</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6124,7 +5866,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D7" s="46" t="n">
         <v>3</v>
@@ -6137,10 +5879,10 @@
         <v>9</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6148,7 +5890,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D8" s="44" t="n">
         <v>3</v>
@@ -6161,10 +5903,10 @@
         <v>6</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6172,7 +5914,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D9" s="46" t="n">
         <v>3</v>
@@ -6185,10 +5927,10 @@
         <v>9</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6196,7 +5938,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D10" s="44" t="n">
         <v>2</v>
@@ -6209,10 +5951,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6220,7 +5962,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D11" s="46" t="n">
         <v>2</v>
@@ -6233,10 +5975,10 @@
         <v>4</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6244,7 +5986,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D12" s="44" t="n">
         <v>3</v>
@@ -6257,10 +5999,10 @@
         <v>6</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6268,7 +6010,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D13" s="46" t="n">
         <v>1</v>
@@ -6281,10 +6023,10 @@
         <v>4</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -6327,148 +6069,148 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -6502,105 +6244,105 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C11" s="48" t="n">
-        <f aca="false">'المحفظة المقترحة'!G24</f>
-        <v>0.05819666</v>
+        <f aca="false">'المحفظة المقترحة'!G21</f>
+        <v>0.0570245266666667</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -6633,222 +6375,222 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="10" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="10" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="10" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="10" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="10" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="10" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="10" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="10" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="10" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="10" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>

--- a/waqf-2026/محفظة-الوقف-2026.xlsx
+++ b/waqf-2026/محفظة-الوقف-2026.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="447">
   <si>
-    <t xml:space="preserve">المحفظة المعتمدة من مجلس الإدارة — 1,500,000 ريال</t>
+    <t xml:space="preserve">المحفظة المعتمدة — 1,500,000 ريال</t>
   </si>
   <si>
     <t xml:space="preserve">الأسعار: آخر إغلاق على أرقام في 11–12 أكتوبر 2026 · الخلايا الزرقاء مدخلات قابلة للتعديل وتعيد حساب كل شيء تلقائياً</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">مستبعد</t>
   </si>
   <si>
-    <t xml:space="preserve">استُبعد بقرار مجلس الإدارة (أكتوبر 2026)</t>
+    <t xml:space="preserve">نمو بطيء وتراجع السعر 16% خلال 6 أشهر</t>
   </si>
   <si>
     <t xml:space="preserve">بنك الجزيرة</t>
@@ -629,6 +629,9 @@
     <t xml:space="preserve">~100%</t>
   </si>
   <si>
+    <t xml:space="preserve">يوزع ~100% من أرباحه دون هامش أمان</t>
+  </si>
+  <si>
     <t xml:space="preserve">بوبا العربية</t>
   </si>
   <si>
@@ -809,10 +812,10 @@
     <t xml:space="preserve">ملاحظات</t>
   </si>
   <si>
-    <t xml:space="preserve">اعتماد سياسة الاستثمار والتوزيع (الورقة: سياسة الوقف) من الناظر ومجلس الجمعية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ناظر الوقف / مجلس الجمعية</t>
+    <t xml:space="preserve">اعتماد سياسة الاستثمار والتوزيع (الورقة: سياسة الوقف) من ناظر الوقف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ناظر الوقف</t>
   </si>
   <si>
     <t xml:space="preserve">لم يبدأ</t>
@@ -851,9 +854,6 @@
     <t xml:space="preserve">توثيق/تسجيل الوقف لدى الهيئة العامة للأوقاف وإرفاق كشف المحفظة</t>
   </si>
   <si>
-    <t xml:space="preserve">ناظر الوقف</t>
-  </si>
-  <si>
     <t xml:space="preserve">شهادة تسجيل</t>
   </si>
   <si>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">الأدوات المسموحة</t>
   </si>
   <si>
-    <t xml:space="preserve">أسهم سعودية متوافقة شرعياً (8 أسهم معتمدة من مجلس الإدارة)</t>
+    <t xml:space="preserve">أسهم سعودية متوافقة شرعياً (8 أسهم)</t>
   </si>
   <si>
     <t xml:space="preserve">طلب المتبرع + تنويع مصدر الدخل</t>
@@ -2602,11 +2602,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="97491667"/>
-        <c:axId val="36363071"/>
+        <c:axId val="88347056"/>
+        <c:axId val="23675612"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97491667"/>
+        <c:axId val="88347056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2638,7 +2638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36363071"/>
+        <c:crossAx val="23675612"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2646,7 +2646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36363071"/>
+        <c:axId val="23675612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2688,7 +2688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97491667"/>
+        <c:crossAx val="88347056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4987,18 +4987,18 @@
         <v>103</v>
       </c>
       <c r="Q25" s="35" t="s">
-        <v>104</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>141.3</v>
@@ -5011,7 +5011,7 @@
         <v>0.0283085633404105</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>141</v>
@@ -5020,7 +5020,7 @@
         <v>101</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>83</v>
@@ -5038,15 +5038,15 @@
         <v>103</v>
       </c>
       <c r="Q26" s="32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>40</v>
@@ -5062,16 +5062,16 @@
         <v>0.0341619887730553</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I27" s="17" t="s">
         <v>149</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L27" s="17" t="s">
         <v>83</v>
@@ -5086,21 +5086,21 @@
         <v>3</v>
       </c>
       <c r="P27" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q27" s="35" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>43.5</v>
@@ -5113,7 +5113,7 @@
         <v>0.0264367816091954</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>141</v>
@@ -5122,7 +5122,7 @@
         <v>154</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>83</v>
@@ -5140,18 +5140,18 @@
         <v>103</v>
       </c>
       <c r="Q28" s="32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>6.65</v>
@@ -5164,16 +5164,16 @@
         <v>0.083609022556391</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L29" s="17" t="s">
         <v>83</v>
@@ -5188,21 +5188,21 @@
         <v>2</v>
       </c>
       <c r="P29" s="36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q29" s="35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>8.31</v>
@@ -5215,13 +5215,13 @@
         <v>0.0962695547533093</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>141</v>
@@ -5242,18 +5242,18 @@
         <v>103</v>
       </c>
       <c r="Q30" s="32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>7.79</v>
@@ -5266,13 +5266,13 @@
         <v>0.0693196405648267</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K31" s="17" t="s">
         <v>141</v>
@@ -5293,18 +5293,18 @@
         <v>103</v>
       </c>
       <c r="Q31" s="35" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>4.31</v>
@@ -5317,13 +5317,13 @@
         <v>0.074245939675174</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>141</v>
@@ -5344,18 +5344,18 @@
         <v>103</v>
       </c>
       <c r="Q32" s="32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>4.47</v>
@@ -5368,10 +5368,10 @@
         <v>0.0782997762863535</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>141</v>
@@ -5395,7 +5395,7 @@
         <v>103</v>
       </c>
       <c r="Q33" s="35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +5438,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5465,25 +5465,25 @@
         <v>8</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5491,10 +5491,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E6" s="40" t="n">
         <v>46308</v>
@@ -5503,13 +5503,13 @@
         <v>46315</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5517,10 +5517,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>46308</v>
@@ -5529,13 +5529,13 @@
         <v>46317</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5543,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E8" s="40" t="n">
         <v>46309</v>
@@ -5555,13 +5555,13 @@
         <v>46320</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5569,10 +5569,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>46315</v>
@@ -5581,7 +5581,7 @@
         <v>46341</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>275</v>
@@ -5607,7 +5607,7 @@
         <v>46328</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>279</v>
@@ -5633,7 +5633,7 @@
         <v>46338</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>283</v>
@@ -5659,7 +5659,7 @@
         <v>46371</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>279</v>
@@ -5676,7 +5676,7 @@
         <v>287</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>46402</v>
@@ -5685,7 +5685,7 @@
         <v>46418</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>288</v>
@@ -5711,7 +5711,7 @@
         <v>46477</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>292</v>
@@ -5737,7 +5737,7 @@
         <v>46507</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>296</v>
